--- a/artfynd/A 65419-2021 artfynd.xlsx
+++ b/artfynd/A 65419-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120427543</v>
+        <v>120427541</v>
       </c>
       <c r="B2" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120427541</v>
+        <v>120427543</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 65419-2021 artfynd.xlsx
+++ b/artfynd/A 65419-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120427541</v>
+        <v>120427543</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120427543</v>
+        <v>120427541</v>
       </c>
       <c r="B3" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 65419-2021 artfynd.xlsx
+++ b/artfynd/A 65419-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120427543</v>
+        <v>120427541</v>
       </c>
       <c r="B2" t="n">
-        <v>90662</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -774,108 +769,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>120427541</v>
-      </c>
-      <c r="B3" t="n">
-        <v>78566</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Björnmyran, Ång</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>576977</v>
-      </c>
-      <c r="R3" t="n">
-        <v>7013831</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Helgum</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 65419-2021 artfynd.xlsx
+++ b/artfynd/A 65419-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,8 +774,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120427541</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>